--- a/data_u1/data_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_2025-08-15_LSR3_H.xlsx
@@ -2806,7 +2806,7 @@
         <v>-5.7</v>
       </c>
       <c r="AW6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>-5.5</v>
       </c>
       <c r="BF6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>-7</v>
       </c>
       <c r="AW7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>-7.3</v>
       </c>
       <c r="BF7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>-6.4</v>
       </c>
       <c r="AW8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>-6.2</v>
       </c>
       <c r="BF8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescents)</t>
+          <t>NCT04072354 (2019, adolescent)</t>
         </is>
       </c>
       <c r="C9">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescents) - ulotaront</t>
+          <t>NCT04072354 (2019, adolescent) - ulotaront</t>
         </is>
       </c>
       <c r="EN9">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescents)</t>
+          <t>NCT04072354 (2019, adolescent)</t>
         </is>
       </c>
       <c r="C10">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="EM10" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescents) - ulotaront</t>
+          <t>NCT04072354 (2019, adolescent) - ulotaront</t>
         </is>
       </c>
       <c r="EN10">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescents)</t>
+          <t>NCT04072354 (2019, adolescent)</t>
         </is>
       </c>
       <c r="C11">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="EM11" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescents) - ulotaront</t>
+          <t>NCT04072354 (2019, adolescent) - ulotaront</t>
         </is>
       </c>
       <c r="EN11">
@@ -4522,7 +4522,7 @@
         <v>-5.2</v>
       </c>
       <c r="AW12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>-6</v>
       </c>
       <c r="BF12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
@@ -4590,6 +4590,12 @@
         <v>18</v>
       </c>
       <c r="DK12">
+        <v>155</v>
+      </c>
+      <c r="DL12">
+        <v>6</v>
+      </c>
+      <c r="DM12">
         <v>155</v>
       </c>
       <c r="DT12">
@@ -4839,7 +4845,7 @@
         <v>-5.5</v>
       </c>
       <c r="AW13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -4874,7 +4880,7 @@
         <v>-6.4</v>
       </c>
       <c r="BF13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
@@ -4907,6 +4913,12 @@
         <v>17</v>
       </c>
       <c r="DK13">
+        <v>154</v>
+      </c>
+      <c r="DL13">
+        <v>5</v>
+      </c>
+      <c r="DM13">
         <v>154</v>
       </c>
       <c r="DT13">
@@ -5156,7 +5168,7 @@
         <v>-4.6</v>
       </c>
       <c r="AW14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
@@ -5191,7 +5203,7 @@
         <v>-4.5</v>
       </c>
       <c r="BF14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
@@ -5224,6 +5236,12 @@
         <v>14</v>
       </c>
       <c r="DK14">
+        <v>155</v>
+      </c>
+      <c r="DL14">
+        <v>2</v>
+      </c>
+      <c r="DM14">
         <v>155</v>
       </c>
       <c r="DT14">
@@ -9052,7 +9070,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, monotherapy)</t>
+          <t>NCT03669640 (2018)</t>
         </is>
       </c>
       <c r="C32">
@@ -9366,7 +9384,7 @@
       </c>
       <c r="EM32" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, monotherapy) - ulotaront</t>
+          <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
       <c r="EN32">
@@ -9381,7 +9399,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, monotherapy)</t>
+          <t>NCT03669640 (2018)</t>
         </is>
       </c>
       <c r="C33">
@@ -9695,7 +9713,7 @@
       </c>
       <c r="EM33" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, monotherapy) - ulotaront</t>
+          <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
       <c r="EN33">

--- a/data_u1/data_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_2025-08-15_LSR3_H.xlsx
@@ -1032,12 +1032,12 @@
       </c>
       <c r="EF1" s="1" t="inlineStr">
         <is>
-          <t>schizophrenia_e</t>
+          <t>psychosis_e</t>
         </is>
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
-          <t>schizophrenia_n</t>
+          <t>psychosis_n</t>
         </is>
       </c>
       <c r="EH1" s="1" t="inlineStr">
@@ -1359,6 +1359,15 @@
       <c r="DX2">
         <v>2</v>
       </c>
+      <c r="DY2">
+        <v>25</v>
+      </c>
+      <c r="EF2">
+        <v>6</v>
+      </c>
+      <c r="EG2">
+        <v>25</v>
+      </c>
       <c r="EH2" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
@@ -1681,6 +1690,12 @@
       <c r="DY3">
         <v>14</v>
       </c>
+      <c r="EF3">
+        <v>2</v>
+      </c>
+      <c r="EG3">
+        <v>14</v>
+      </c>
       <c r="EH3" t="inlineStr">
         <is>
           <t>placebo</t>
@@ -8467,7 +8482,7 @@
         </is>
       </c>
       <c r="S30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>201</v>
@@ -8798,7 +8813,7 @@
         </is>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T31">
         <v>102</v>

--- a/data_u1/data_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_2025-08-15_LSR3_H.xlsx
@@ -1133,7 +1133,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.400000000000006</t>
         </is>
       </c>
       <c r="N2">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="N3">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N4">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="N5">
@@ -2821,7 +2821,7 @@
         <v>-5.7</v>
       </c>
       <c r="AW6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>-5.5</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>-7</v>
       </c>
       <c r="AW7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>-7.3</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3503,7 +3503,7 @@
         <v>-6.4</v>
       </c>
       <c r="AW8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>-6.2</v>
       </c>
       <c r="BF8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescent)</t>
+          <t>NCT04072354 (2019):adolescents</t>
         </is>
       </c>
       <c r="C9">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescent) - ulotaront</t>
+          <t>NCT04072354 (2019):adolescents - ulotaront</t>
         </is>
       </c>
       <c r="EN9">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescent)</t>
+          <t>NCT04072354 (2019):adolescents</t>
         </is>
       </c>
       <c r="C10">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="EM10" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescent) - ulotaront</t>
+          <t>NCT04072354 (2019):adolescents - ulotaront</t>
         </is>
       </c>
       <c r="EN10">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescent)</t>
+          <t>NCT04072354 (2019):adolescents</t>
         </is>
       </c>
       <c r="C11">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="EM11" t="inlineStr">
         <is>
-          <t>NCT04072354 (2019, adolescent) - ulotaront</t>
+          <t>NCT04072354 (2019):adolescents - ulotaront</t>
         </is>
       </c>
       <c r="EN11">
@@ -4537,7 +4537,7 @@
         <v>-5.2</v>
       </c>
       <c r="AW12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>-6</v>
       </c>
       <c r="BF12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>-5.5</v>
       </c>
       <c r="AW13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>-6.4</v>
       </c>
       <c r="BF13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>-4.6</v>
       </c>
       <c r="AW14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>-4.5</v>
       </c>
       <c r="BF14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.200000000000003</t>
         </is>
       </c>
       <c r="N15">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N16">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>32.299999999999997</t>
         </is>
       </c>
       <c r="N17">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="N18">
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="S30">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="T30">
         <v>201</v>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some concerns</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="DA30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="DB30">
@@ -8669,7 +8669,7 @@
         <v>201</v>
       </c>
       <c r="DF30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DG30">
         <v>201</v>
@@ -8717,7 +8717,7 @@
         <v>201</v>
       </c>
       <c r="EF30">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="EG30">
         <v>201</v>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T31">
         <v>102</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some concerns</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="DA31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="DB31">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon)</t>
+          <t>NCT03669640 (2018):addon</t>
         </is>
       </c>
       <c r="C34">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="EM34" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - ulotaront</t>
+          <t>NCT03669640 (2018):addon - ulotaront</t>
         </is>
       </c>
       <c r="EN34">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon)</t>
+          <t>NCT03669640 (2018):addon</t>
         </is>
       </c>
       <c r="C35">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="EM35" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - ulotaront</t>
+          <t>NCT03669640 (2018):addon - ulotaront</t>
         </is>
       </c>
       <c r="EN35">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon)</t>
+          <t>NCT03669640 (2018):addon</t>
         </is>
       </c>
       <c r="C36">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="EM36" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - ulotaront</t>
+          <t>NCT03669640 (2018):addon - ulotaront</t>
         </is>
       </c>
       <c r="EN36">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon)</t>
+          <t>NCT03669640 (2018):addon</t>
         </is>
       </c>
       <c r="C37">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="EM37" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - ulotaront</t>
+          <t>NCT03669640 (2018):addon - ulotaront</t>
         </is>
       </c>
       <c r="EN37">

--- a/data_u1/data_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_2025-08-15_LSR3_H.xlsx
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="DB6">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="DC6">
         <v>144</v>
@@ -2934,7 +2934,7 @@
         <v>144</v>
       </c>
       <c r="EF6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="EG6">
         <v>144</v>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="DB7">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="DC7">
         <v>145</v>
@@ -3275,7 +3275,7 @@
         <v>145</v>
       </c>
       <c r="EF7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="EG7">
         <v>145</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="DB8">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="DC8">
         <v>146</v>
@@ -3616,7 +3616,7 @@
         <v>146</v>
       </c>
       <c r="EF8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="EG8">
         <v>146</v>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="DB12">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="DC12">
         <v>155</v>
@@ -4632,7 +4632,7 @@
         <v>155</v>
       </c>
       <c r="EF12">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="EG12">
         <v>155</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="DB13">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="DC13">
         <v>154</v>
@@ -4955,7 +4955,7 @@
         <v>154</v>
       </c>
       <c r="EF13">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="EG13">
         <v>154</v>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="DB14">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="DC14">
         <v>155</v>
@@ -5278,7 +5278,7 @@
         <v>155</v>
       </c>
       <c r="EF14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="EG14">
         <v>155</v>
@@ -6352,7 +6352,7 @@
         <v>68</v>
       </c>
       <c r="EF17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG17">
         <v>68</v>

--- a/data_u1/data_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_2025-08-15_LSR3_H.xlsx
@@ -11193,7 +11193,7 @@
         </is>
       </c>
       <c r="EN38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="EN39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
